--- a/data/AttributeDimension.xlsx
+++ b/data/AttributeDimension.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -710,29 +710,29 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>金相</t>
+          <t>体质</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>金相:影响金系法伤、人物法伤。</t>
+          <t>体质:提高宝宝气血上限和防御。</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -741,49 +741,49 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>木相</t>
+          <t>灵力</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>木相:影响木系法伤、人物气血、法力。</t>
+          <t>灵力:提高宝宝法力上限和法伤。</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -794,26 +794,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>水相</t>
+          <t>力量</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>水相:影响水系法伤、人物防御。</t>
+          <t>力量:提高宝宝物伤。</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -831,31 +831,31 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>204</v>
+        <v>404</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>火相</t>
+          <t>敏捷</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>火相:影响火系法伤、人物速度。</t>
+          <t>敏捷:提高宝宝出手速度。</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -870,387 +870,9 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>205</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>土相</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>土相:影响土系法伤、人物物伤。</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>60</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>301</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>仙攻</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>仙攻:大幅提高法伤。</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>160</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>302</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>仙护</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>仙护:大幅提高防御。</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>303</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>魔攻</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>魔攻:大幅提高物伤。</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>120</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>304</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>魔体</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>魔体:大幅提高气血上限。</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>167</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>401</v>
-      </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>体质</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>体质:提高宝宝气血上限和防御。</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>42</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>402</v>
-      </c>
-      <c r="B20" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>灵力</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>灵力:提高宝宝法力上限和法伤。</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>33</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>403</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>力量</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>力量:提高宝宝物伤。</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>40</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>404</v>
-      </c>
-      <c r="B22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>敏捷</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>敏捷:提高宝宝出手速度。</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L22" t="n">
         <v>0</v>
       </c>
     </row>
